--- a/Result/profitability/2353.xlsx
+++ b/Result/profitability/2353.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0.465</v>
+        <v>0.4925</v>
       </c>
       <c r="N2" t="n">
-        <v>10.7775</v>
+        <v>10.87875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0.55375</v>
+        <v>0.58375</v>
       </c>
       <c r="N3" t="n">
-        <v>10.80375</v>
+        <v>10.9075</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6487499999999999</v>
+        <v>0.7175</v>
       </c>
       <c r="N4" t="n">
-        <v>10.7475</v>
+        <v>10.84875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.76875</v>
+        <v>0.8137500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>10.75375</v>
+        <v>10.91125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.78</v>
       </c>
       <c r="M6" t="n">
-        <v>0.82125</v>
+        <v>0.865</v>
       </c>
       <c r="N6" t="n">
-        <v>10.74125</v>
+        <v>10.7675</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.89</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8862500000000001</v>
+        <v>0.93125</v>
       </c>
       <c r="N7" t="n">
-        <v>10.665</v>
+        <v>10.64125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.00625</v>
+        <v>1.0675</v>
       </c>
       <c r="N8" t="n">
-        <v>10.4675</v>
+        <v>10.49375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>85303</v>
+      </c>
+      <c r="D75" t="n">
+        <v>75603</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9701</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1783</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2107</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3890</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2172</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.8775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.130434782608695</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.2099999999999991</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01881720430107525</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1246290801186944</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
